--- a/Sample/참석자업로드_샘플.xlsx
+++ b/Sample/참석자업로드_샘플.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\dev\startour\convention\Sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E745DA-C05F-4BD0-9A6D-4ED9A5AC7008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088EB11D-D506-4DF5-B9AD-BCC8167FE7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF7BFAF7-7A20-4F6C-9DD2-1AC299AE6969}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FF7BFAF7-7A20-4F6C-9DD2-1AC299AE6969}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="참석자" sheetId="5" r:id="rId1"/>
+    <sheet name="그룹-일정 매핑" sheetId="4" r:id="rId2"/>
+    <sheet name="속성" sheetId="6" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$5</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,97 +27,171 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
+  <si>
+    <t>010-2734-8926</t>
+  </si>
+  <si>
+    <t>010-9019-3989</t>
+  </si>
+  <si>
+    <t>그룹명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정코스명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차</t>
+  </si>
+  <si>
+    <t>1차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차</t>
+  </si>
+  <si>
+    <t>2차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>티셔츠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>선발대</t>
+  </si>
+  <si>
+    <t>선발대</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
   <si>
     <t>번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>이름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주민번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>연락처</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그룹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>STAFF</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>정유진</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>870119-2</t>
   </si>
   <si>
     <t>엄범식</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>860526-1</t>
+  </si>
+  <si>
+    <t>010-4187-1867</t>
   </si>
   <si>
     <t>김도현</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>020823-3</t>
+  </si>
+  <si>
+    <t>010-6675-4147</t>
   </si>
   <si>
     <t>노정은</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>주민번호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>연락처</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-2734-8926</t>
-  </si>
-  <si>
-    <t>010-4187-1867</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-6675-4147</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-9019-3989</t>
-  </si>
-  <si>
-    <t>870119-2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>860526-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>020823-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>811202-2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>부서</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>그룹</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1차</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>선발대</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>한식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>양식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1일차 선호 식사</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알레르기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>땅콩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌석선호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>창가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>복도</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상관없음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상연락처</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-9999-1111</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-9999-2222</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-9999-2223</t>
+  </si>
+  <si>
+    <t>010-9999-2224</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,69 +222,21 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="나눔고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="나눔고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -223,35 +248,526 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{3F225B9E-B9C0-4CB5-BAF2-3CC979C286F7}"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="78">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -898,185 +1414,268 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D978733-F40D-43C2-BC78-5D1AACE7A082}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB852B96-7C07-4701-9A27-09EEF5157131}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.69921875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.19921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="F5" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection autoFilter="0"/>
-  <autoFilter ref="A1:E5" xr:uid="{4D978733-F40D-43C2-BC78-5D1AACE7A082}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1:E1048576">
-    <cfRule type="cellIs" dxfId="26" priority="121" operator="equal">
-      <formula>"값 없음"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:E1048576 A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="224"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
-    <cfRule type="duplicateValues" dxfId="24" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="179"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3">
-    <cfRule type="duplicateValues" dxfId="22" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="173"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="duplicateValues" dxfId="20" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="171"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:E1048576 D1:F1">
-    <cfRule type="cellIs" dxfId="18" priority="55" operator="equal">
-      <formula>"불참"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="17" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="229"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="duplicateValues" dxfId="15" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="231"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:F2">
-    <cfRule type="duplicateValues" dxfId="13" priority="226"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="227"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F5">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
-      <formula>"값 없음"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="10" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="0" priority="233"/>
-  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4650ED1-B635-485A-8845-518721CE1327}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E68F047C-168B-4307-BA70-9D2B57D36F6E}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3">
+        <v>110</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>